--- a/output-app/Neraca Lajur 2026.xlsx
+++ b/output-app/Neraca Lajur 2026.xlsx
@@ -405,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L15"/>
   <cols>
     <col min="1" max="1" width="35.83203125" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" customWidth="1"/>
@@ -654,7 +654,7 @@
         <v/>
       </c>
       <c r="G7">
-        <v>2230800</v>
+        <v>1905800</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -712,45 +712,273 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>Persediaan Bahan Kimia</v>
+      </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9">
+        <v>125644</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Persediaan Bahan Instalasi</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10">
+        <v>21696230000.28</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Utang Usaha</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11">
+        <v>125000</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Utang Usaha - Bahan Kimia</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12">
+        <v>125000</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Kekayaan Pemda Yang Dipisahkan</v>
+      </c>
+      <c r="B13" t="str">
+        <v/>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13">
+        <v>21696230644.28</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
         <v>Pendapatan Denda</v>
       </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9">
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14">
         <v>1085400</v>
       </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Pemeliharaan Kendaraan</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15">
+        <v>200000</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output-app/Neraca Lajur 2026.xlsx
+++ b/output-app/Neraca Lajur 2026.xlsx
@@ -32,7 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
@@ -42,6 +42,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -405,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <cols>
     <col min="1" max="1" width="35.83203125" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" customWidth="1"/>
@@ -654,7 +655,7 @@
         <v/>
       </c>
       <c r="G7">
-        <v>1905800</v>
+        <v>4405200</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -695,7 +696,7 @@
         <v/>
       </c>
       <c r="H8">
-        <v>1145400</v>
+        <v>2672600</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -730,7 +731,7 @@
         <v/>
       </c>
       <c r="G9">
-        <v>125644</v>
+        <v>502576</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -768,7 +769,7 @@
         <v/>
       </c>
       <c r="G10">
-        <v>21696230000.28</v>
+        <v>86784920001.11</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -806,7 +807,7 @@
         <v/>
       </c>
       <c r="G11">
-        <v>125000</v>
+        <v>500000</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -847,7 +848,7 @@
         <v/>
       </c>
       <c r="H12">
-        <v>125000</v>
+        <v>500000</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -885,7 +886,7 @@
         <v/>
       </c>
       <c r="H13">
-        <v>21696230644.28</v>
+        <v>86784922577.11</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -902,7 +903,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Pendapatan Denda</v>
+        <v>Pendapatan Harga Air</v>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -929,7 +930,7 @@
         <v/>
       </c>
       <c r="J14">
-        <v>1085400</v>
+        <v>500000</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -940,45 +941,83 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>Pendapatan Denda</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15">
+        <v>2532600</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
         <v>Pemeliharaan Kendaraan</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15">
-        <v>200000</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16">
+        <v>800000</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/output-app/Neraca Lajur 2026.xlsx
+++ b/output-app/Neraca Lajur 2026.xlsx
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L15"/>
   <cols>
     <col min="1" max="1" width="35.83203125" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" customWidth="1"/>
@@ -655,7 +655,7 @@
         <v/>
       </c>
       <c r="G7">
-        <v>4405200</v>
+        <v>837200</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -696,7 +696,7 @@
         <v/>
       </c>
       <c r="H8">
-        <v>2672600</v>
+        <v>763600</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -731,7 +731,7 @@
         <v/>
       </c>
       <c r="G9">
-        <v>502576</v>
+        <v>251288</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -769,7 +769,7 @@
         <v/>
       </c>
       <c r="G10">
-        <v>86784920001.11</v>
+        <v>43392460000.55</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -807,7 +807,7 @@
         <v/>
       </c>
       <c r="G11">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -848,7 +848,7 @@
         <v/>
       </c>
       <c r="H12">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="H13">
-        <v>86784922577.11</v>
+        <v>43392461288.55</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -903,7 +903,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Pendapatan Harga Air</v>
+        <v>Pendapatan Denda</v>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -930,7 +930,7 @@
         <v/>
       </c>
       <c r="J14">
-        <v>500000</v>
+        <v>723600</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -941,7 +941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Pendapatan Denda</v>
+        <v>Pemeliharaan Kendaraan</v>
       </c>
       <c r="B15" t="str">
         <v/>
@@ -964,60 +964,22 @@
       <c r="H15" t="str">
         <v/>
       </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15">
-        <v>2532600</v>
+      <c r="I15">
+        <v>400000</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
       </c>
       <c r="K15" t="str">
         <v/>
       </c>
       <c r="L15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Pemeliharaan Kendaraan</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16">
-        <v>800000</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>